--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K708"/>
+  <dimension ref="A1:K710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28048,6 +28048,84 @@
         <v>396.6</v>
       </c>
       <c r="K708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:06+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="C709" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="D709" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="E709" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="F709" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="G709" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="H709" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="I709" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="J709" t="n">
+        <v>390.79</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="C710" t="n">
+        <v>361.12</v>
+      </c>
+      <c r="D710" t="n">
+        <v>369.18</v>
+      </c>
+      <c r="E710" t="n">
+        <v>370.93</v>
+      </c>
+      <c r="F710" t="n">
+        <v>368.59</v>
+      </c>
+      <c r="G710" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="H710" t="n">
+        <v>359.75</v>
+      </c>
+      <c r="I710" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="J710" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="K710" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28064,7 +28142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B719"/>
+  <dimension ref="A1:B721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35257,6 +35335,26 @@
       </c>
       <c r="B719" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -35425,28 +35523,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2674995406578202</v>
+        <v>0.2620935015458459</v>
       </c>
       <c r="J2" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K2" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08630503138561774</v>
+        <v>0.08315246403478549</v>
       </c>
       <c r="M2" t="n">
-        <v>5.080430353802306</v>
+        <v>5.088727784191787</v>
       </c>
       <c r="N2" t="n">
-        <v>40.00389575188407</v>
+        <v>40.13654476548003</v>
       </c>
       <c r="O2" t="n">
-        <v>6.32486329906695</v>
+        <v>6.335340935220458</v>
       </c>
       <c r="P2" t="n">
-        <v>364.7833926400787</v>
+        <v>364.8403426877541</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35503,28 +35601,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001196981616111823</v>
+        <v>-0.005934891935011465</v>
       </c>
       <c r="J3" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K3" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L3" t="n">
-        <v>2.009945909708932e-08</v>
+        <v>4.93189538097738e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.89453295556438</v>
+        <v>4.910655570967065</v>
       </c>
       <c r="N3" t="n">
-        <v>37.64277809701988</v>
+        <v>37.84389542744817</v>
       </c>
       <c r="O3" t="n">
-        <v>6.135371064330166</v>
+        <v>6.151739219720564</v>
       </c>
       <c r="P3" t="n">
-        <v>371.1805305870889</v>
+        <v>371.2443134082752</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35581,28 +35679,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05601174918591855</v>
+        <v>0.05279122831839456</v>
       </c>
       <c r="J4" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K4" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004668835257004234</v>
+        <v>0.004165417662662541</v>
       </c>
       <c r="M4" t="n">
-        <v>4.634873590941286</v>
+        <v>4.635665185811456</v>
       </c>
       <c r="N4" t="n">
-        <v>35.31900095914583</v>
+        <v>35.30674341081187</v>
       </c>
       <c r="O4" t="n">
-        <v>5.942979131643138</v>
+        <v>5.941947779206063</v>
       </c>
       <c r="P4" t="n">
-        <v>373.7348432882512</v>
+        <v>373.7687721839598</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35659,28 +35757,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1255896920681896</v>
+        <v>0.1215435063063577</v>
       </c>
       <c r="J5" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K5" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02791054025256201</v>
+        <v>0.02622690697878227</v>
       </c>
       <c r="M5" t="n">
-        <v>4.163037336689676</v>
+        <v>4.172384763800527</v>
       </c>
       <c r="N5" t="n">
-        <v>29.00928798131211</v>
+        <v>29.0656268258823</v>
       </c>
       <c r="O5" t="n">
-        <v>5.386027105512198</v>
+        <v>5.391254661568335</v>
       </c>
       <c r="P5" t="n">
-        <v>375.2796323493941</v>
+        <v>375.3222600188423</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35737,28 +35835,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04228219362459715</v>
+        <v>-0.04388788555161846</v>
       </c>
       <c r="J6" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K6" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003648679550147582</v>
+        <v>0.003951253157492118</v>
       </c>
       <c r="M6" t="n">
-        <v>4.07214596380208</v>
+        <v>4.069182862320333</v>
       </c>
       <c r="N6" t="n">
-        <v>25.77999842723809</v>
+        <v>25.73004409878915</v>
       </c>
       <c r="O6" t="n">
-        <v>5.077400755035797</v>
+        <v>5.072479088058339</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1278685339245</v>
+        <v>373.1447860615676</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35815,28 +35913,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1212696376909632</v>
+        <v>-0.1237165168144774</v>
       </c>
       <c r="J7" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K7" t="n">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02379816743593821</v>
+        <v>0.02485807682752239</v>
       </c>
       <c r="M7" t="n">
-        <v>4.525490530602165</v>
+        <v>4.524100929200596</v>
       </c>
       <c r="N7" t="n">
-        <v>31.69858794124171</v>
+        <v>31.66025657887268</v>
       </c>
       <c r="O7" t="n">
-        <v>5.630149903976066</v>
+        <v>5.626744758639109</v>
       </c>
       <c r="P7" t="n">
-        <v>368.003177992034</v>
+        <v>368.0290457735163</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35893,28 +35991,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1040810378558635</v>
+        <v>-0.1041507303491171</v>
       </c>
       <c r="J8" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K8" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01434368578342782</v>
+        <v>0.01445221123241403</v>
       </c>
       <c r="M8" t="n">
-        <v>4.96011133089749</v>
+        <v>4.946592630488132</v>
       </c>
       <c r="N8" t="n">
-        <v>39.30963949381913</v>
+        <v>39.19886609624496</v>
       </c>
       <c r="O8" t="n">
-        <v>6.269739986141302</v>
+        <v>6.260899783277557</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7675810695989</v>
+        <v>362.7683157269902</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35971,28 +36069,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2267053318504728</v>
+        <v>-0.2278372026974908</v>
       </c>
       <c r="J9" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K9" t="n">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05978784494117384</v>
+        <v>0.06069414442574506</v>
       </c>
       <c r="M9" t="n">
-        <v>5.307588665139992</v>
+        <v>5.297678987011721</v>
       </c>
       <c r="N9" t="n">
-        <v>42.68907459585449</v>
+        <v>42.57954344116028</v>
       </c>
       <c r="O9" t="n">
-        <v>6.533687672046659</v>
+        <v>6.525300256782081</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0125377315405</v>
+        <v>367.0244675998954</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36049,28 +36147,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05420608491841526</v>
+        <v>-0.05273537229757563</v>
       </c>
       <c r="J10" t="n">
+        <v>709</v>
+      </c>
+      <c r="K10" t="n">
         <v>707</v>
       </c>
-      <c r="K10" t="n">
-        <v>705</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002943687517210081</v>
+        <v>0.002803219825222358</v>
       </c>
       <c r="M10" t="n">
-        <v>5.908782838830533</v>
+        <v>5.898666075444992</v>
       </c>
       <c r="N10" t="n">
-        <v>52.30545803088123</v>
+        <v>52.17549568990705</v>
       </c>
       <c r="O10" t="n">
-        <v>7.232251242239945</v>
+        <v>7.223260738053629</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5989888689653</v>
+        <v>389.5834359140233</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36108,7 +36206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K708"/>
+  <dimension ref="A1:K710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76451,6 +76549,120 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:06+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-37.38130649632633,175.93744969221433</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-37.382005576876274,175.93763186987783</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-37.38265933414913,175.93798782721893</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-37.38331466850973,175.93831366449226</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-37.38396014708268,175.9386733899817</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-37.38462784036219,175.93900469779837</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>-37.38526338347867,175.93941523556913</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>-37.38591459158255,175.93977027597742</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>-37.38633335996242,175.94056986650764</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-37.38130405217296,175.93746195609768</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-37.38200354707161,175.9376408855699</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-37.38266204959182,175.9379781366851</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-37.38331938881619,175.93830036071049</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-37.38396560324042,175.93866040797135</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-37.384634170706214,175.9389903834011</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-37.38526473829942,175.9394119204202</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>-37.385917797876694,175.939763473238</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>-37.38633420834235,175.94056840674662</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K710"/>
+  <dimension ref="A1:K712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28126,6 +28126,84 @@
         <v>390.63</v>
       </c>
       <c r="K710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="C711" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="D711" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="E711" t="n">
+        <v>371.14</v>
+      </c>
+      <c r="F711" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="G711" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="H711" t="n">
+        <v>360.36</v>
+      </c>
+      <c r="I711" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="J711" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="C712" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="D712" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="E712" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="F712" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="G712" t="n">
+        <v>361.96</v>
+      </c>
+      <c r="H712" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="I712" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="J712" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="K712" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28142,7 +28220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B721"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35355,6 +35433,26 @@
       </c>
       <c r="B721" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -35523,28 +35621,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2620935015458459</v>
+        <v>0.2570637018015132</v>
       </c>
       <c r="J2" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K2" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08315246403478549</v>
+        <v>0.08031791025566948</v>
       </c>
       <c r="M2" t="n">
-        <v>5.088727784191787</v>
+        <v>5.095336930748093</v>
       </c>
       <c r="N2" t="n">
-        <v>40.13654476548003</v>
+        <v>40.23688167173753</v>
       </c>
       <c r="O2" t="n">
-        <v>6.335340935220458</v>
+        <v>6.343254816869454</v>
       </c>
       <c r="P2" t="n">
-        <v>364.8403426877541</v>
+        <v>364.8934507310883</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35601,28 +35699,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.005934891935011465</v>
+        <v>-0.01111287698493535</v>
       </c>
       <c r="J3" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K3" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L3" t="n">
-        <v>4.93189538097738e-05</v>
+        <v>0.0001729521270803502</v>
       </c>
       <c r="M3" t="n">
-        <v>4.910655570967065</v>
+        <v>4.922831356867447</v>
       </c>
       <c r="N3" t="n">
-        <v>37.84389542744817</v>
+        <v>37.96378107401431</v>
       </c>
       <c r="O3" t="n">
-        <v>6.151739219720564</v>
+        <v>6.161475559800129</v>
       </c>
       <c r="P3" t="n">
-        <v>371.2443134082752</v>
+        <v>371.2989860402841</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35679,28 +35777,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05279122831839456</v>
+        <v>0.04939998206212649</v>
       </c>
       <c r="J4" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004165417662662541</v>
+        <v>0.003662275274773474</v>
       </c>
       <c r="M4" t="n">
-        <v>4.635665185811456</v>
+        <v>4.637120350981639</v>
       </c>
       <c r="N4" t="n">
-        <v>35.30674341081187</v>
+        <v>35.30422194988489</v>
       </c>
       <c r="O4" t="n">
-        <v>5.941947779206063</v>
+        <v>5.941735600805954</v>
       </c>
       <c r="P4" t="n">
-        <v>373.7687721839598</v>
+        <v>373.8045793352726</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35757,28 +35855,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1215435063063577</v>
+        <v>0.1173884025805677</v>
       </c>
       <c r="J5" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K5" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02622690697878227</v>
+        <v>0.0245385407393991</v>
       </c>
       <c r="M5" t="n">
-        <v>4.172384763800527</v>
+        <v>4.182370438921223</v>
       </c>
       <c r="N5" t="n">
-        <v>29.0656268258823</v>
+        <v>29.12924583851274</v>
       </c>
       <c r="O5" t="n">
-        <v>5.391254661568335</v>
+        <v>5.397151641237509</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3222600188423</v>
+        <v>375.3661324682967</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35835,28 +35933,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04388788555161846</v>
+        <v>-0.04556772733259282</v>
       </c>
       <c r="J6" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K6" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003951253157492118</v>
+        <v>0.004281013711227244</v>
       </c>
       <c r="M6" t="n">
-        <v>4.069182862320333</v>
+        <v>4.066589740222637</v>
       </c>
       <c r="N6" t="n">
-        <v>25.73004409878915</v>
+        <v>25.68161789715652</v>
       </c>
       <c r="O6" t="n">
-        <v>5.072479088058339</v>
+        <v>5.067703414482395</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1447860615676</v>
+        <v>373.1625229174885</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35913,28 +36011,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1237165168144774</v>
+        <v>-0.1256937797005493</v>
       </c>
       <c r="J7" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K7" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02485807682752239</v>
+        <v>0.0257698483836204</v>
       </c>
       <c r="M7" t="n">
-        <v>4.524100929200596</v>
+        <v>4.520582479517465</v>
       </c>
       <c r="N7" t="n">
-        <v>31.66025657887268</v>
+        <v>31.60477721978189</v>
       </c>
       <c r="O7" t="n">
-        <v>5.626744758639109</v>
+        <v>5.621812627594581</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0290457735163</v>
+        <v>368.0499941861697</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35991,28 +36089,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1041507303491171</v>
+        <v>-0.1036729989215278</v>
       </c>
       <c r="J8" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K8" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01445221123241403</v>
+        <v>0.014410058348442</v>
       </c>
       <c r="M8" t="n">
-        <v>4.946592630488132</v>
+        <v>4.934873357794064</v>
       </c>
       <c r="N8" t="n">
-        <v>39.19886609624496</v>
+        <v>39.09122849753868</v>
       </c>
       <c r="O8" t="n">
-        <v>6.260899783277557</v>
+        <v>6.252297857391207</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7683157269902</v>
+        <v>362.7632713254139</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36069,28 +36167,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2278372026974908</v>
+        <v>-0.2282256940900933</v>
       </c>
       <c r="J9" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K9" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06069414442574506</v>
+        <v>0.06124707509215288</v>
       </c>
       <c r="M9" t="n">
-        <v>5.297678987011721</v>
+        <v>5.284487445383795</v>
       </c>
       <c r="N9" t="n">
-        <v>42.57954344116028</v>
+        <v>42.46149795456904</v>
       </c>
       <c r="O9" t="n">
-        <v>6.525300256782081</v>
+        <v>6.516248764018225</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0244675998954</v>
+        <v>367.0285710758369</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36147,28 +36245,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05273537229757563</v>
+        <v>-0.05207765315635916</v>
       </c>
       <c r="J10" t="n">
+        <v>711</v>
+      </c>
+      <c r="K10" t="n">
         <v>709</v>
       </c>
-      <c r="K10" t="n">
-        <v>707</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002803219825222358</v>
+        <v>0.002750988784897657</v>
       </c>
       <c r="M10" t="n">
-        <v>5.898666075444992</v>
+        <v>5.884981947635129</v>
       </c>
       <c r="N10" t="n">
-        <v>52.17549568990705</v>
+        <v>52.03193212632887</v>
       </c>
       <c r="O10" t="n">
-        <v>7.223260738053629</v>
+        <v>7.213316305717425</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5834359140233</v>
+        <v>389.5764646318921</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36206,7 +36304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K710"/>
+  <dimension ref="A1:K712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76663,6 +76761,120 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-37.38130481597102,175.93745812363423</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-37.38200237320836,175.93764609946385</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-37.38266187055168,175.93797877562142</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-37.383318620394306,175.9383025264425</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-37.38396472186119,175.93866250506548</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-37.384630416157535,175.93899887331978</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-37.38526223393374,175.93941804842262</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>-37.38591262200166,175.9397744548028</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>-37.386341101428656,175.94055654618697</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-37.381303375666,175.93746535056525</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-37.38199997657021,175.93765674449676</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-37.382661691511515,175.93797941455773</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-37.38331744946565,175.93830582660553</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-37.38396245545728,175.93866789759295</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-37.38462508993633,175.9390109171564</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-37.38525812841556,175.93942809432733</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>-37.38590831640576,175.9397835899086</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>-37.386341101428656,175.94055654618697</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K712"/>
+  <dimension ref="A1:K713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28206,6 +28206,45 @@
       <c r="K712" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-03 21:59:54+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="C713" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="D713" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="E713" t="n">
+        <v>370.43</v>
+      </c>
+      <c r="F713" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="G713" t="n">
+        <v>361.85</v>
+      </c>
+      <c r="H713" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="I713" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="J713" t="n">
+        <v>389.87</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35453,6 +35492,16 @@
       </c>
       <c r="B723" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-02-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -35621,28 +35670,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2570637018015132</v>
+        <v>0.254554193968976</v>
       </c>
       <c r="J2" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K2" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08031791025566948</v>
+        <v>0.07891865583836333</v>
       </c>
       <c r="M2" t="n">
-        <v>5.095336930748093</v>
+        <v>5.098565574976289</v>
       </c>
       <c r="N2" t="n">
-        <v>40.23688167173753</v>
+        <v>40.2863721412029</v>
       </c>
       <c r="O2" t="n">
-        <v>6.343254816869454</v>
+        <v>6.347154649226919</v>
       </c>
       <c r="P2" t="n">
-        <v>364.8934507310883</v>
+        <v>364.9200230439541</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35699,28 +35748,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01111287698493535</v>
+        <v>-0.01370257705469766</v>
       </c>
       <c r="J3" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K3" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001729521270803502</v>
+        <v>0.0002629779148380917</v>
       </c>
       <c r="M3" t="n">
-        <v>4.922831356867447</v>
+        <v>4.92913168696488</v>
       </c>
       <c r="N3" t="n">
-        <v>37.96378107401431</v>
+        <v>38.02334707029407</v>
       </c>
       <c r="O3" t="n">
-        <v>6.161475559800129</v>
+        <v>6.166307409649155</v>
       </c>
       <c r="P3" t="n">
-        <v>371.2989860402841</v>
+        <v>371.3264074810903</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35777,28 +35826,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04939998206212649</v>
+        <v>0.04753558230628422</v>
       </c>
       <c r="J4" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K4" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003662275274773474</v>
+        <v>0.003397056219837769</v>
       </c>
       <c r="M4" t="n">
-        <v>4.637120350981639</v>
+        <v>4.638534806677529</v>
       </c>
       <c r="N4" t="n">
-        <v>35.30422194988489</v>
+        <v>35.31314585845844</v>
       </c>
       <c r="O4" t="n">
-        <v>5.941735600805954</v>
+        <v>5.942486504693001</v>
       </c>
       <c r="P4" t="n">
-        <v>373.8045793352726</v>
+        <v>373.8243208212233</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35855,28 +35904,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1173884025805677</v>
+        <v>0.1150734562341601</v>
       </c>
       <c r="J5" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K5" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0245385407393991</v>
+        <v>0.02360434615331919</v>
       </c>
       <c r="M5" t="n">
-        <v>4.182370438921223</v>
+        <v>4.188511415121603</v>
       </c>
       <c r="N5" t="n">
-        <v>29.12924583851274</v>
+        <v>29.1785373279723</v>
       </c>
       <c r="O5" t="n">
-        <v>5.397151641237509</v>
+        <v>5.401716146556787</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3661324682967</v>
+        <v>375.3906446366934</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35933,28 +35982,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04556772733259282</v>
+        <v>-0.04639290760158844</v>
       </c>
       <c r="J6" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K6" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004281013711227244</v>
+        <v>0.004448771499227178</v>
       </c>
       <c r="M6" t="n">
-        <v>4.066589740222637</v>
+        <v>4.065195606188098</v>
       </c>
       <c r="N6" t="n">
-        <v>25.68161789715652</v>
+        <v>25.65700963061198</v>
       </c>
       <c r="O6" t="n">
-        <v>5.067703414482395</v>
+        <v>5.065274882038682</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1625229174885</v>
+        <v>373.1712604667379</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36011,28 +36060,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1256937797005493</v>
+        <v>-0.1265293172871281</v>
       </c>
       <c r="J7" t="n">
+        <v>712</v>
+      </c>
+      <c r="K7" t="n">
         <v>711</v>
       </c>
-      <c r="K7" t="n">
-        <v>710</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0257698483836204</v>
+        <v>0.02617583819066283</v>
       </c>
       <c r="M7" t="n">
-        <v>4.520582479517465</v>
+        <v>4.518142313752921</v>
       </c>
       <c r="N7" t="n">
-        <v>31.60477721978189</v>
+        <v>31.5719917020786</v>
       </c>
       <c r="O7" t="n">
-        <v>5.621812627594581</v>
+        <v>5.618895950458471</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0499941861697</v>
+        <v>368.0588715099725</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36089,28 +36138,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1036729989215278</v>
+        <v>-0.1031512678430539</v>
       </c>
       <c r="J8" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K8" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L8" t="n">
-        <v>0.014410058348442</v>
+        <v>0.01431030206809458</v>
       </c>
       <c r="M8" t="n">
-        <v>4.934873357794064</v>
+        <v>4.930322142565216</v>
       </c>
       <c r="N8" t="n">
-        <v>39.09122849753868</v>
+        <v>39.04090686670413</v>
       </c>
       <c r="O8" t="n">
-        <v>6.252297857391207</v>
+        <v>6.248272310543462</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7632713254139</v>
+        <v>362.7577468949781</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36167,28 +36216,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2282256940900933</v>
+        <v>-0.2279013650211409</v>
       </c>
       <c r="J9" t="n">
+        <v>712</v>
+      </c>
+      <c r="K9" t="n">
         <v>711</v>
       </c>
-      <c r="K9" t="n">
-        <v>710</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.06124707509215288</v>
+        <v>0.06126272101551045</v>
       </c>
       <c r="M9" t="n">
-        <v>5.284487445383795</v>
+        <v>5.278770930925798</v>
       </c>
       <c r="N9" t="n">
-        <v>42.46149795456904</v>
+        <v>42.4035489788899</v>
       </c>
       <c r="O9" t="n">
-        <v>6.516248764018225</v>
+        <v>6.511800747787811</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0285710758369</v>
+        <v>367.0251354475614</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36245,28 +36294,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05207765315635916</v>
+        <v>-0.05159425068612083</v>
       </c>
       <c r="J10" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K10" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002750988784897657</v>
+        <v>0.002708626929373237</v>
       </c>
       <c r="M10" t="n">
-        <v>5.884981947635129</v>
+        <v>5.878852817305197</v>
       </c>
       <c r="N10" t="n">
-        <v>52.03193212632887</v>
+        <v>51.96255520687233</v>
       </c>
       <c r="O10" t="n">
-        <v>7.213316305717425</v>
+        <v>7.20850575409858</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5764646318921</v>
+        <v>389.5713264698181</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36304,7 +36353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K712"/>
+  <dimension ref="A1:K713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76875,6 +76924,63 @@
         </is>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-03 21:59:54+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-37.381304161286984,175.9374614086029</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-37.38200134607783,175.9376506616209</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-37.382663660953064,175.93797238625808</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-37.38332121839196,175.93829520420545</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-37.383963462747936,175.9386655009141</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-37.38462557016945,175.93900983123677</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-37.38525615776655,175.93943291636114</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>-37.38590231605293,175.93979632074576</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>-37.38633823814679,175.94056147288126</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K713"/>
+  <dimension ref="A1:K714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28245,6 +28245,45 @@
       <c r="K713" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="C714" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="D714" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="E714" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="F714" t="n">
+        <v>370.36</v>
+      </c>
+      <c r="G714" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="H714" t="n">
+        <v>364.69</v>
+      </c>
+      <c r="I714" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="J714" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28259,7 +28298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B724"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35502,6 +35541,16 @@
       </c>
       <c r="B724" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -35670,28 +35719,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.254554193968976</v>
+        <v>0.2525669171097435</v>
       </c>
       <c r="J2" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K2" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07891865583836333</v>
+        <v>0.07789964328482546</v>
       </c>
       <c r="M2" t="n">
-        <v>5.098565574976289</v>
+        <v>5.099596409748716</v>
       </c>
       <c r="N2" t="n">
-        <v>40.2863721412029</v>
+        <v>40.29554040625558</v>
       </c>
       <c r="O2" t="n">
-        <v>6.347154649226919</v>
+        <v>6.347876842398219</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9200230439541</v>
+        <v>364.941161697654</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35748,28 +35797,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01370257705469766</v>
+        <v>-0.01656788127272832</v>
       </c>
       <c r="J3" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K3" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002629779148380917</v>
+        <v>0.000384263261867801</v>
       </c>
       <c r="M3" t="n">
-        <v>4.92913168696488</v>
+        <v>4.936689147395169</v>
       </c>
       <c r="N3" t="n">
-        <v>38.02334707029407</v>
+        <v>38.10653881869997</v>
       </c>
       <c r="O3" t="n">
-        <v>6.166307409649155</v>
+        <v>6.173049393832838</v>
       </c>
       <c r="P3" t="n">
-        <v>371.3264074810903</v>
+        <v>371.3568857072762</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35826,28 +35875,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04753558230628422</v>
+        <v>0.04515616530499113</v>
       </c>
       <c r="J4" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K4" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003397056219837769</v>
+        <v>0.00306814678949896</v>
       </c>
       <c r="M4" t="n">
-        <v>4.638534806677529</v>
+        <v>4.642043373469444</v>
       </c>
       <c r="N4" t="n">
-        <v>35.31314585845844</v>
+        <v>35.35776330840254</v>
       </c>
       <c r="O4" t="n">
-        <v>5.942486504693001</v>
+        <v>5.946239425754949</v>
       </c>
       <c r="P4" t="n">
-        <v>373.8243208212233</v>
+        <v>373.8496306675914</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35904,28 +35953,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1150734562341601</v>
+        <v>0.1124852195988469</v>
       </c>
       <c r="J5" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K5" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02360434615331919</v>
+        <v>0.02256467805334594</v>
       </c>
       <c r="M5" t="n">
-        <v>4.188511415121603</v>
+        <v>4.195955854040842</v>
       </c>
       <c r="N5" t="n">
-        <v>29.1785373279723</v>
+        <v>29.24900830763487</v>
       </c>
       <c r="O5" t="n">
-        <v>5.401716146556787</v>
+        <v>5.408235230427286</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3906446366934</v>
+        <v>375.4181756964314</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35982,28 +36031,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04639290760158844</v>
+        <v>-0.04685121933051712</v>
       </c>
       <c r="J6" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K6" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004448771499227178</v>
+        <v>0.004550578691431828</v>
       </c>
       <c r="M6" t="n">
-        <v>4.065195606188098</v>
+        <v>4.061865862388493</v>
       </c>
       <c r="N6" t="n">
-        <v>25.65700963061198</v>
+        <v>25.62451788011148</v>
       </c>
       <c r="O6" t="n">
-        <v>5.065274882038682</v>
+        <v>5.062066562196855</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1712604667379</v>
+        <v>373.1761355262342</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36060,28 +36109,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1265293172871281</v>
+        <v>-0.1267824967171847</v>
       </c>
       <c r="J7" t="n">
+        <v>713</v>
+      </c>
+      <c r="K7" t="n">
         <v>712</v>
       </c>
-      <c r="K7" t="n">
-        <v>711</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02617583819066283</v>
+        <v>0.02635938550048789</v>
       </c>
       <c r="M7" t="n">
-        <v>4.518142313752921</v>
+        <v>4.512970371705307</v>
       </c>
       <c r="N7" t="n">
-        <v>31.5719917020786</v>
+        <v>31.52870714756879</v>
       </c>
       <c r="O7" t="n">
-        <v>5.618895950458471</v>
+        <v>5.615042933724442</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0588715099725</v>
+        <v>368.061573688553</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36138,28 +36187,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1031512678430539</v>
+        <v>-0.1017989599502789</v>
       </c>
       <c r="J8" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K8" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01431030206809458</v>
+        <v>0.01397611526321851</v>
       </c>
       <c r="M8" t="n">
-        <v>4.930322142565216</v>
+        <v>4.92950676936247</v>
       </c>
       <c r="N8" t="n">
-        <v>39.04090686670413</v>
+        <v>39.01656039953241</v>
       </c>
       <c r="O8" t="n">
-        <v>6.248272310543462</v>
+        <v>6.246323750777925</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7577468949781</v>
+        <v>362.7433624028988</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36216,28 +36265,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2279013650211409</v>
+        <v>-0.2259924113017802</v>
       </c>
       <c r="J9" t="n">
+        <v>713</v>
+      </c>
+      <c r="K9" t="n">
         <v>712</v>
       </c>
-      <c r="K9" t="n">
-        <v>711</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.06126272101551045</v>
+        <v>0.0604028067104535</v>
       </c>
       <c r="M9" t="n">
-        <v>5.278770930925798</v>
+        <v>5.281346264884665</v>
       </c>
       <c r="N9" t="n">
-        <v>42.4035489788899</v>
+        <v>42.40463216134806</v>
       </c>
       <c r="O9" t="n">
-        <v>6.511800747787811</v>
+        <v>6.511883917987794</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0251354475614</v>
+        <v>367.0048213829852</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36294,28 +36343,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05159425068612083</v>
+        <v>-0.05413361382188672</v>
       </c>
       <c r="J10" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K10" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002708626929373237</v>
+        <v>0.002984448010809992</v>
       </c>
       <c r="M10" t="n">
-        <v>5.878852817305197</v>
+        <v>5.883879250664974</v>
       </c>
       <c r="N10" t="n">
-        <v>51.96255520687233</v>
+        <v>51.99599052192686</v>
       </c>
       <c r="O10" t="n">
-        <v>7.20850575409858</v>
+        <v>7.210824538284569</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5713264698181</v>
+        <v>389.5984406364494</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36353,7 +36402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K713"/>
+  <dimension ref="A1:K714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76981,6 +77030,63 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-37.38130014588955,175.9374815564094</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-37.38200366934902,175.93764034245592</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-37.3826689426352,175.93795353763434</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-37.383324584810794,175.93828571623547</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-37.38395817447149,175.93867808347727</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-37.38461688231448,175.93902947650776</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>-37.38524445703419,175.93946154718165</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>-37.385877398543386,175.93984918771125</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>-37.3863933297776,175.94046667956695</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K714"/>
+  <dimension ref="A1:K716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28282,6 +28282,84 @@
         <v>379.48</v>
       </c>
       <c r="K714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="C715" t="n">
+        <v>362.71</v>
+      </c>
+      <c r="D715" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="E715" t="n">
+        <v>369.81</v>
+      </c>
+      <c r="F715" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="G715" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="H715" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="I715" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="J715" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="C716" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="D716" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="E716" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="F716" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="G716" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="H716" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="I716" t="n">
+        <v>366.46</v>
+      </c>
+      <c r="J716" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="K716" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28298,7 +28376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35551,6 +35629,26 @@
       </c>
       <c r="B725" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -35719,28 +35817,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2525669171097435</v>
+        <v>0.2489888159565715</v>
       </c>
       <c r="J2" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K2" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07789964328482546</v>
+        <v>0.07613977261819227</v>
       </c>
       <c r="M2" t="n">
-        <v>5.099596409748716</v>
+        <v>5.100018805278468</v>
       </c>
       <c r="N2" t="n">
-        <v>40.29554040625558</v>
+        <v>40.28928611769885</v>
       </c>
       <c r="O2" t="n">
-        <v>6.347876842398219</v>
+        <v>6.347384194902562</v>
       </c>
       <c r="P2" t="n">
-        <v>364.941161697654</v>
+        <v>364.9793215157538</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35797,28 +35895,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01656788127272832</v>
+        <v>-0.02100241545308006</v>
       </c>
       <c r="J3" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K3" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000384263261867801</v>
+        <v>0.0006186559398950742</v>
       </c>
       <c r="M3" t="n">
-        <v>4.936689147395169</v>
+        <v>4.945091406974145</v>
       </c>
       <c r="N3" t="n">
-        <v>38.10653881869997</v>
+        <v>38.16416264477713</v>
       </c>
       <c r="O3" t="n">
-        <v>6.173049393832838</v>
+        <v>6.177715001906217</v>
       </c>
       <c r="P3" t="n">
-        <v>371.3568857072762</v>
+        <v>371.4041772830834</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35875,28 +35973,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04515616530499113</v>
+        <v>0.04081100741786933</v>
       </c>
       <c r="J4" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K4" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00306814678949896</v>
+        <v>0.00251245390369359</v>
       </c>
       <c r="M4" t="n">
-        <v>4.642043373469444</v>
+        <v>4.647587072337085</v>
       </c>
       <c r="N4" t="n">
-        <v>35.35776330840254</v>
+        <v>35.41597541172635</v>
       </c>
       <c r="O4" t="n">
-        <v>5.946239425754949</v>
+        <v>5.9511322798041</v>
       </c>
       <c r="P4" t="n">
-        <v>373.8496306675914</v>
+        <v>373.8959705114472</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35953,28 +36051,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1124852195988469</v>
+        <v>0.1080156111397056</v>
       </c>
       <c r="J5" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K5" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02256467805334594</v>
+        <v>0.02085756936398397</v>
       </c>
       <c r="M5" t="n">
-        <v>4.195955854040842</v>
+        <v>4.207372199319761</v>
       </c>
       <c r="N5" t="n">
-        <v>29.24900830763487</v>
+        <v>29.3352926828367</v>
       </c>
       <c r="O5" t="n">
-        <v>5.408235230427286</v>
+        <v>5.41620648450894</v>
       </c>
       <c r="P5" t="n">
-        <v>375.4181756964314</v>
+        <v>375.4658394136811</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36031,28 +36129,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04685121933051712</v>
+        <v>-0.04721306555725568</v>
       </c>
       <c r="J6" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K6" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004550578691431828</v>
+        <v>0.004649867917923101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.061865862388493</v>
+        <v>4.053094666724387</v>
       </c>
       <c r="N6" t="n">
-        <v>25.62451788011148</v>
+        <v>25.55611648845347</v>
       </c>
       <c r="O6" t="n">
-        <v>5.062066562196855</v>
+        <v>5.055305775959894</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1761355262342</v>
+        <v>373.1799894466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36109,28 +36207,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1267824967171847</v>
+        <v>-0.1273152811907717</v>
       </c>
       <c r="J7" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K7" t="n">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02635938550048789</v>
+        <v>0.02674067322415608</v>
       </c>
       <c r="M7" t="n">
-        <v>4.512970371705307</v>
+        <v>4.502777860869717</v>
       </c>
       <c r="N7" t="n">
-        <v>31.52870714756879</v>
+        <v>31.44273340514955</v>
       </c>
       <c r="O7" t="n">
-        <v>5.615042933724442</v>
+        <v>5.607382045585048</v>
       </c>
       <c r="P7" t="n">
-        <v>368.061573688553</v>
+        <v>368.0672749678939</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36187,28 +36285,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1017989599502789</v>
+        <v>-0.09937189295560427</v>
       </c>
       <c r="J8" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K8" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01397611526321851</v>
+        <v>0.01339438377381785</v>
       </c>
       <c r="M8" t="n">
-        <v>4.92950676936247</v>
+        <v>4.926719922135048</v>
       </c>
       <c r="N8" t="n">
-        <v>39.01656039953241</v>
+        <v>38.95679032281753</v>
       </c>
       <c r="O8" t="n">
-        <v>6.246323750777925</v>
+        <v>6.241537496708446</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7433624028988</v>
+        <v>362.717479772533</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36265,28 +36363,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2259924113017802</v>
+        <v>-0.2224820093745423</v>
       </c>
       <c r="J9" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K9" t="n">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0604028067104535</v>
+        <v>0.05886996299111646</v>
       </c>
       <c r="M9" t="n">
-        <v>5.281346264884665</v>
+        <v>5.284771768788236</v>
       </c>
       <c r="N9" t="n">
-        <v>42.40463216134806</v>
+        <v>42.38941312570604</v>
       </c>
       <c r="O9" t="n">
-        <v>6.511883917987794</v>
+        <v>6.510715254540474</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0048213829852</v>
+        <v>366.9673704061518</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36343,28 +36441,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05413361382188672</v>
+        <v>-0.06058618520354334</v>
       </c>
       <c r="J10" t="n">
+        <v>715</v>
+      </c>
+      <c r="K10" t="n">
         <v>713</v>
       </c>
-      <c r="K10" t="n">
-        <v>711</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002984448010809992</v>
+        <v>0.003734301221226644</v>
       </c>
       <c r="M10" t="n">
-        <v>5.883879250664974</v>
+        <v>5.901433019251579</v>
       </c>
       <c r="N10" t="n">
-        <v>51.99599052192686</v>
+        <v>52.20194165835373</v>
       </c>
       <c r="O10" t="n">
-        <v>7.210824538284569</v>
+        <v>7.225091117650609</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5984406364494</v>
+        <v>389.6675097040452</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36402,7 +36500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K714"/>
+  <dimension ref="A1:K716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77087,6 +77185,120 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-37.381299098394024,175.93748681235854</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-37.381999658648745,175.93765815659293</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-37.382667808715,175.93795758423178</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-37.383323487065596,175.93828881013883</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-37.38395792264876,175.93867868264692</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-37.384617187917485,175.93902878546814</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>-37.38524474442069,175.93946084396862</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>-37.38587680308792,175.93985045107578</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>-37.38641517552502,175.94042909064865</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-37.38129837824071,175.93749042582348</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-37.38199709082098,175.93766956198445</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-37.382666167514444,175.93796344114887</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-37.38331722991652,175.9383064453861</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-37.38395049387724,175.9386963581491</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-37.384617144259906,175.9390288841881</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>-37.385247864616574,175.939453209084</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>-37.38588248281645,175.93983840052087</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>-37.38639741260017,175.94045965445528</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K716"/>
+  <dimension ref="A1:K719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28360,6 +28360,123 @@
         <v>378.71</v>
       </c>
       <c r="K716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="C717" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="D717" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="E717" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="F717" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="G717" t="n">
+        <v>364.7</v>
+      </c>
+      <c r="H717" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="I717" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="J717" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="C718" t="n">
+        <v>365.72</v>
+      </c>
+      <c r="D718" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="E718" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="F718" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="G718" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="H718" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="I718" t="n">
+        <v>362.8</v>
+      </c>
+      <c r="J718" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="C719" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="D719" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="E719" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="F719" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="G719" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="H719" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="I719" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="J719" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="K719" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28376,7 +28493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35649,6 +35766,46 @@
       </c>
       <c r="B727" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -35817,28 +35974,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2489888159565715</v>
+        <v>0.2442396613869632</v>
       </c>
       <c r="J2" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K2" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07613977261819227</v>
+        <v>0.07391954611389906</v>
       </c>
       <c r="M2" t="n">
-        <v>5.100018805278468</v>
+        <v>5.098249272392519</v>
       </c>
       <c r="N2" t="n">
-        <v>40.28928611769885</v>
+        <v>40.2464596650842</v>
       </c>
       <c r="O2" t="n">
-        <v>6.347384194902562</v>
+        <v>6.34400974661012</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9793215157538</v>
+        <v>365.030153481074</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35895,28 +36052,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02100241545308006</v>
+        <v>-0.02567645966536393</v>
       </c>
       <c r="J3" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K3" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006186559398950742</v>
+        <v>0.000930316900032202</v>
       </c>
       <c r="M3" t="n">
-        <v>4.945091406974145</v>
+        <v>4.947823475969869</v>
       </c>
       <c r="N3" t="n">
-        <v>38.16416264477713</v>
+        <v>38.12773725213098</v>
       </c>
       <c r="O3" t="n">
-        <v>6.177715001906217</v>
+        <v>6.174766169834368</v>
       </c>
       <c r="P3" t="n">
-        <v>371.4041772830834</v>
+        <v>371.4541982330243</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35973,28 +36130,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04081100741786933</v>
+        <v>0.03533013917660931</v>
       </c>
       <c r="J4" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K4" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00251245390369359</v>
+        <v>0.001893395549313781</v>
       </c>
       <c r="M4" t="n">
-        <v>4.647587072337085</v>
+        <v>4.651810682477915</v>
       </c>
       <c r="N4" t="n">
-        <v>35.41597541172635</v>
+        <v>35.43497675498314</v>
       </c>
       <c r="O4" t="n">
-        <v>5.9511322798041</v>
+        <v>5.952728513461969</v>
       </c>
       <c r="P4" t="n">
-        <v>373.8959705114472</v>
+        <v>373.9546330428471</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36051,28 +36208,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1080156111397056</v>
+        <v>0.1031405533976128</v>
       </c>
       <c r="J5" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K5" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02085756936398397</v>
+        <v>0.0191484931561664</v>
       </c>
       <c r="M5" t="n">
-        <v>4.207372199319761</v>
+        <v>4.215356292824985</v>
       </c>
       <c r="N5" t="n">
-        <v>29.3352926828367</v>
+        <v>29.3449553146117</v>
       </c>
       <c r="O5" t="n">
-        <v>5.41620648450894</v>
+        <v>5.41709842209016</v>
       </c>
       <c r="P5" t="n">
-        <v>375.4658394136811</v>
+        <v>375.5180169243253</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36129,28 +36286,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04721306555725568</v>
+        <v>-0.04588542931371745</v>
       </c>
       <c r="J6" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K6" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004649867917923101</v>
+        <v>0.004433844150696697</v>
       </c>
       <c r="M6" t="n">
-        <v>4.053094666724387</v>
+        <v>4.042074851967605</v>
       </c>
       <c r="N6" t="n">
-        <v>25.55611648845347</v>
+        <v>25.4592249201389</v>
       </c>
       <c r="O6" t="n">
-        <v>5.055305775959894</v>
+        <v>5.04571351942804</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1799894466</v>
+        <v>373.1657806284013</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36207,28 +36364,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1273152811907717</v>
+        <v>-0.1274811719373247</v>
       </c>
       <c r="J7" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K7" t="n">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02674067322415608</v>
+        <v>0.02706174548838258</v>
       </c>
       <c r="M7" t="n">
-        <v>4.502777860869717</v>
+        <v>4.484747225055609</v>
       </c>
       <c r="N7" t="n">
-        <v>31.44273340514955</v>
+        <v>31.31141716547345</v>
       </c>
       <c r="O7" t="n">
-        <v>5.607382045585048</v>
+        <v>5.595660565605589</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0672749678939</v>
+        <v>368.06905821315</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36285,28 +36442,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09937189295560427</v>
+        <v>-0.09726162400072465</v>
       </c>
       <c r="J8" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K8" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01339438377381785</v>
+        <v>0.0129521348008248</v>
       </c>
       <c r="M8" t="n">
-        <v>4.926719922135048</v>
+        <v>4.915651666240628</v>
       </c>
       <c r="N8" t="n">
-        <v>38.95679032281753</v>
+        <v>38.82270301777734</v>
       </c>
       <c r="O8" t="n">
-        <v>6.241537496708446</v>
+        <v>6.230786709379269</v>
       </c>
       <c r="P8" t="n">
-        <v>362.717479772533</v>
+        <v>362.6949036026679</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36363,28 +36520,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2224820093745423</v>
+        <v>-0.2203744954607589</v>
       </c>
       <c r="J9" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K9" t="n">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05886996299111646</v>
+        <v>0.05830267174378434</v>
       </c>
       <c r="M9" t="n">
-        <v>5.284771768788236</v>
+        <v>5.27348654144533</v>
       </c>
       <c r="N9" t="n">
-        <v>42.38941312570604</v>
+        <v>42.24967070503318</v>
       </c>
       <c r="O9" t="n">
-        <v>6.510715254540474</v>
+        <v>6.499974669568581</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9673704061518</v>
+        <v>366.9448228850132</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36441,28 +36598,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06058618520354334</v>
+        <v>-0.06506774203253553</v>
       </c>
       <c r="J10" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K10" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003734301221226644</v>
+        <v>0.004336319631105923</v>
       </c>
       <c r="M10" t="n">
-        <v>5.901433019251579</v>
+        <v>5.900379413664399</v>
       </c>
       <c r="N10" t="n">
-        <v>52.20194165835373</v>
+        <v>52.10387234394816</v>
       </c>
       <c r="O10" t="n">
-        <v>7.225091117650609</v>
+        <v>7.21830120900674</v>
       </c>
       <c r="P10" t="n">
-        <v>389.6675097040452</v>
+        <v>389.7156447790563</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36500,7 +36657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K716"/>
+  <dimension ref="A1:K719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77299,6 +77456,177 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-37.38129728709913,175.9374959007702</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-37.38199513438007,175.93767825180598</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>-37.38266410855336,175.9379707889172</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>-37.38331382690455,175.9383160364842</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>-37.38394445012904,175.938710738216</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>-37.38461312776315,175.93903796642238</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>-37.385247905671775,175.939453108625</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>-37.38588504785474,175.9398329583341</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>-37.38638463389447,175.94048164213993</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>-37.38129791996128,175.9374927253011</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>-37.38199229753963,175.93769085204633</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>-37.382663780313145,175.9379719603005</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>-37.38331302189087,175.93831830534597</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>-37.38394499574527,175.9387094400156</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>-37.38461448114801,175.93903490610444</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>-37.38525488505564,175.9394360305912</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>-37.385899247169675,175.93980283193648</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>-37.38637641522282,175.94049578359284</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>-37.38129676335109,175.93749852874456</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>-37.38199171060696,175.93769345899247</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>-37.38266327303279,175.93797377062018</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>-37.383312033919466,175.9383210898581</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>-37.38394596106625,175.93870714319948</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>-37.38461461212072,175.9390346099446</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>-37.38525730731183,175.9394301035081</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>-37.385904010809206,175.93979272501332</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>-37.38636501512727,175.94051539915134</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K719"/>
+  <dimension ref="A1:K722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28477,6 +28477,123 @@
         <v>384.82</v>
       </c>
       <c r="K719" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>367.93</v>
+      </c>
+      <c r="C720" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="D720" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="E720" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="F720" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="G720" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="H720" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="I720" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="J720" t="n">
+        <v>389.82</v>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>366.79</v>
+      </c>
+      <c r="C721" t="n">
+        <v>368</v>
+      </c>
+      <c r="D721" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="E721" t="n">
+        <v>375.37</v>
+      </c>
+      <c r="F721" t="n">
+        <v>374.83</v>
+      </c>
+      <c r="G721" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="H721" t="n">
+        <v>363.05</v>
+      </c>
+      <c r="I721" t="n">
+        <v>362.91</v>
+      </c>
+      <c r="J721" t="n">
+        <v>394.13</v>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="C722" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="D722" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="E722" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="F722" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="G722" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="H722" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="I722" t="n">
+        <v>361.28</v>
+      </c>
+      <c r="J722" t="n">
+        <v>392.76</v>
+      </c>
+      <c r="K722" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28493,7 +28610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35806,6 +35923,36 @@
       </c>
       <c r="B731" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -35974,28 +36121,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2442396613869632</v>
+        <v>0.2399857272670226</v>
       </c>
       <c r="J2" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K2" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07391954611389906</v>
+        <v>0.07201652890186572</v>
       </c>
       <c r="M2" t="n">
-        <v>5.098249272392519</v>
+        <v>5.094404021069548</v>
       </c>
       <c r="N2" t="n">
-        <v>40.2464596650842</v>
+        <v>40.18547814245902</v>
       </c>
       <c r="O2" t="n">
-        <v>6.34400974661012</v>
+        <v>6.339201695991304</v>
       </c>
       <c r="P2" t="n">
-        <v>365.030153481074</v>
+        <v>365.0758924115126</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36052,28 +36199,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02567645966536393</v>
+        <v>-0.0283453858914978</v>
       </c>
       <c r="J3" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K3" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000930316900032202</v>
+        <v>0.001143322326788709</v>
       </c>
       <c r="M3" t="n">
-        <v>4.947823475969869</v>
+        <v>4.940559940504966</v>
       </c>
       <c r="N3" t="n">
-        <v>38.12773725213098</v>
+        <v>38.00926729698872</v>
       </c>
       <c r="O3" t="n">
-        <v>6.174766169834368</v>
+        <v>6.165165634189298</v>
       </c>
       <c r="P3" t="n">
-        <v>371.4541982330243</v>
+        <v>371.4828914844971</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36130,28 +36277,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03533013917660931</v>
+        <v>0.03115650556389568</v>
       </c>
       <c r="J4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001893395549313781</v>
+        <v>0.001483280060793235</v>
       </c>
       <c r="M4" t="n">
-        <v>4.651810682477915</v>
+        <v>4.65048802437509</v>
       </c>
       <c r="N4" t="n">
-        <v>35.43497675498314</v>
+        <v>35.3850590531039</v>
       </c>
       <c r="O4" t="n">
-        <v>5.952728513461969</v>
+        <v>5.948534193656779</v>
       </c>
       <c r="P4" t="n">
-        <v>373.9546330428471</v>
+        <v>373.9995028112948</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36208,28 +36355,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1031405533976128</v>
+        <v>0.1007106522789665</v>
       </c>
       <c r="J5" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K5" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0191484931561664</v>
+        <v>0.01842682557556952</v>
       </c>
       <c r="M5" t="n">
-        <v>4.215356292824985</v>
+        <v>4.210571223087895</v>
       </c>
       <c r="N5" t="n">
-        <v>29.3449553146117</v>
+        <v>29.25588437742122</v>
       </c>
       <c r="O5" t="n">
-        <v>5.41709842209016</v>
+        <v>5.408870896723384</v>
       </c>
       <c r="P5" t="n">
-        <v>375.5180169243253</v>
+        <v>375.5441402105824</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36286,28 +36433,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04588542931371745</v>
+        <v>-0.04346596140997416</v>
       </c>
       <c r="J6" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K6" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004433844150696697</v>
+        <v>0.004013664752835822</v>
       </c>
       <c r="M6" t="n">
-        <v>4.042074851967605</v>
+        <v>4.03588093558764</v>
       </c>
       <c r="N6" t="n">
-        <v>25.4592249201389</v>
+        <v>25.38640024550433</v>
       </c>
       <c r="O6" t="n">
-        <v>5.04571351942804</v>
+        <v>5.038491862204833</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1657806284013</v>
+        <v>373.1397726112198</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36364,28 +36511,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1274811719373247</v>
+        <v>-0.1252093536045953</v>
       </c>
       <c r="J7" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K7" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02706174548838258</v>
+        <v>0.02635445931716052</v>
       </c>
       <c r="M7" t="n">
-        <v>4.484747225055609</v>
+        <v>4.477513922363657</v>
       </c>
       <c r="N7" t="n">
-        <v>31.31141716547345</v>
+        <v>31.20997236610555</v>
       </c>
       <c r="O7" t="n">
-        <v>5.595660565605589</v>
+        <v>5.586588616150786</v>
       </c>
       <c r="P7" t="n">
-        <v>368.06905821315</v>
+        <v>368.0445555819656</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36442,28 +36589,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09726162400072465</v>
+        <v>-0.09515303475201627</v>
       </c>
       <c r="J8" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K8" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0129521348008248</v>
+        <v>0.01251233684284292</v>
       </c>
       <c r="M8" t="n">
-        <v>4.915651666240628</v>
+        <v>4.904574367067354</v>
       </c>
       <c r="N8" t="n">
-        <v>38.82270301777734</v>
+        <v>38.69267864316818</v>
       </c>
       <c r="O8" t="n">
-        <v>6.230786709379269</v>
+        <v>6.220343932868036</v>
       </c>
       <c r="P8" t="n">
-        <v>362.6949036026679</v>
+        <v>362.6722434529033</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36520,28 +36667,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2203744954607589</v>
+        <v>-0.2189708678783089</v>
       </c>
       <c r="J9" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K9" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05830267174378434</v>
+        <v>0.05811089118705204</v>
       </c>
       <c r="M9" t="n">
-        <v>5.27348654144533</v>
+        <v>5.258619972890312</v>
       </c>
       <c r="N9" t="n">
-        <v>42.24967070503318</v>
+        <v>42.08937825206355</v>
       </c>
       <c r="O9" t="n">
-        <v>6.499974669568581</v>
+        <v>6.487632715564557</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9448228850132</v>
+        <v>366.9297337691289</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36598,28 +36745,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06506774203253553</v>
+        <v>-0.06139444254662631</v>
       </c>
       <c r="J10" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K10" t="n">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004336319631105923</v>
+        <v>0.003893199343896869</v>
       </c>
       <c r="M10" t="n">
-        <v>5.900379413664399</v>
+        <v>5.891683455604372</v>
       </c>
       <c r="N10" t="n">
-        <v>52.10387234394816</v>
+        <v>51.97468690832576</v>
       </c>
       <c r="O10" t="n">
-        <v>7.21830120900674</v>
+        <v>7.209347190164014</v>
       </c>
       <c r="P10" t="n">
-        <v>389.7156447790563</v>
+        <v>389.6759974705781</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36657,7 +36804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K719"/>
+  <dimension ref="A1:K722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77627,6 +77774,177 @@
         </is>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>-37.38129333716453,175.93751572007588</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>-37.38198733306573,175.93771290246443</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>-37.38265879702852,175.93798974402773</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>-37.38330208101884,175.93834914123514</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>-37.38393819652675,175.93872561758823</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>-37.384600903638535,175.93906560799888</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>-37.385248152003015,175.93945250587092</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>-37.38589439192087,175.93981313322215</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>-37.386338503265485,175.94056101670589</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>-37.381295824969015,175.9375032371985</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>-37.38198672167705,175.93771561803294</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>-37.38265897606873,175.93798910509148</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>-37.383303142174,175.9383461504637</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>-37.38393941367095,175.93872272160323</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>-37.384600729008135,175.9390660028785</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>-37.385251190088,175.93944507190363</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>-37.38589874332316,175.93980390093787</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>-37.386315650027505,175.9406003390116</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>-37.381299491204864,175.93748484137762</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>-37.38198865366509,175.9377070368363</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>-37.38266073663063,175.93798282221806</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>-37.383303361723314,175.93834553168338</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>-37.38394151219531,175.93871772852543</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>-37.38460378503989,175.93905909248528</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>-37.38526038645066,175.93942256907988</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>-37.38590620941178,175.93978806027914</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>-37.38632291428313,175.94058783981265</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
